--- a/data/output/2025/evaluasi_11.xlsx
+++ b/data/output/2025/evaluasi_11.xlsx
@@ -25,6 +25,12 @@
     <sheet name="1106" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="1108" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="1101" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="1102" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="1109" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="1172" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="1175" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="1112" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="1173" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1720,7 +1726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1892,6 +1898,258 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.419829190530128</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.464363414224006</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.85932091433318</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>29.05395911825255</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.198025570532204</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.78765277310938</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.05485985431522615</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5.369111319220762</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1906,7 +2164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1994,6 +2252,230 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-5.65977307406618</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>28.18482323818554</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>43.09338713071546</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-7.897151126615948</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10.4401337056759</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4.423851233324768</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7.902188097557921</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2138,20 +2620,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.351367008281361</v>
+        <v>-14.99954746091568</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2166,18 +2648,270 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Gayo Lues</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-13.70331043825832</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Gayo Lues</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Gayo Lues</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.527321045586265</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Gayo Lues</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.047374724322357</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q4-25_prov vs c-to-c_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Gayo Lues</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.38034219002083</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Gayo Lues</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.979648352683141</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Gayo Lues</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8.752450174422105</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Gayo Lues</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.351367008281361</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Gayo Lues</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>-2.913633212138168</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2194,7 +2928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2254,6 +2988,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bener Meriah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.625858228551738</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bener Meriah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.96595333735969</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bener Meriah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>46.51845254551802</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bener Meriah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-7.862154237454642</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bener Meriah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bener Meriah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.01653201836029572</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q4-25_prov vs c-to-c_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bener Meriah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-9.259461863851246</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2268,7 +3198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,6 +3258,146 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie Jaya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>41.84934323931845</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie Jaya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-7.863098149548599</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie Jaya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie Jaya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2577102013362742</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie Jaya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1720577916874439</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q4-25_prov vs c-to-c_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2342,7 +3412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2458,6 +3528,286 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.05808726746877</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.441633012755295</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>51.263591412223</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.69238074836659</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4.070651103986981</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.387395372814778</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>9.100301994196636</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.852314193908042</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5747558828789345</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2472,7 +3822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2602,20 +3952,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.266657992994987</v>
+        <v>1.876002443487742</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2630,18 +3980,186 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>19.08772796435542</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tengah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.03356499477533941</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tengah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.385643767511568</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-6.261161673001101</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.266657992994987</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>2.329447302608446</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2658,7 +4176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2746,6 +4264,174 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Besar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.7500441584231116</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Besar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.198805338109302</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Besar</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Besar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-8.998883194151034</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Besar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-4.169517145994683</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Besar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8.876866407442321</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2760,7 +4446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2806,20 +4492,542 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>4.83891974196494</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.6066410288911251</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9258423919455608</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>42.92264800139852</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4.636347369139513</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.629698847635141</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.194653786059913</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-8.432893259893666</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6.438684277327322</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.01133948712320637</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.341581700166715</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>-2.347278255956059</v>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Singkil</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.06056405989173506</v>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Singkil</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>39.16497296606975</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Singkil</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.477129002483733</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Singkil</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Singkil</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-8.215547392584146</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2834,7 +5042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3090,6 +5298,1356 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.85852288460523</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Timur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-5.926151554312428</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Timur</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Timur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.442816848873888</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3.120201639666782</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.289529775235184</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.28739071415952</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.89303886520264</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9367234074283427</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Sabang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3.823520991373734</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Sabang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3599463680683921</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Sabang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.984167186205143</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Sabang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.549813344947904</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Sabang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.22064911034499</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Sabang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.577617559132285</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Sabang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Sabang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.707680864139367</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Sabang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.287145984146326</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Sabang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.344642339922824</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.104417512367499</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>20.09461897360081</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4861427138064918</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.187650283489866</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-17.16510521445122</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-8.599659911498504</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.466000134647728</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-5.149076447239268</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.207374946817422</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.8212217003462925</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat Daya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>31.49752697380238</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat Daya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.932796020453613</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat Daya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.132637649974074</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat Daya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat Daya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-14.62490951316683</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat Daya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-8.815518297696677</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Langsa</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Langsa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-7.645909633879261</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Langsa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.534235001758047</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3104,7 +6662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3276,6 +6834,258 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.802419192166592</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>26.31521802033587</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.595278414275785</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9325442812685096</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.719185559859366</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.732734417062914</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.225979027018989</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>9.335231092640488</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3290,7 +7100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3462,6 +7272,258 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.597262981156027</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.2114729975949521</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.83633525631906</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>72.00262862544417</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4.191245903017295</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.581168256186996</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-7.418340521171849</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.157882506636189</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3476,7 +7538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4180,6 +8242,286 @@
       <c r="F25" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1.747866874104105</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.5919712110347702</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>15.53637643159355</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.08754603014478204</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>4.312882137585343</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2.749713175874026</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3.318800165849456</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1.008453484336483</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.6646179250845827</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4194,7 +8536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4408,20 +8750,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-3.360251599259862</v>
+        <v>0.5399579921550263</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4436,18 +8778,354 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>-1.771427366055755</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.280259361970367</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>45.24041898230083</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.8871873674087741</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.055010153406536</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.099271228809107</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.726577770679528</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.112564322197851</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4.990394543043323</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.6211387733787244</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-3.360251599259862</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>-2.428349825123618</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -4464,7 +9142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4608,6 +9286,314 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.635795124570087</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.56013939122672</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>24.08217394985515</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4599311694141541</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7220476784024548</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.711188497305105</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-18.59799054019189</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1116720787628526</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-8.716870233204252</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6.466013960700447</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4622,7 +9608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4780,20 +9766,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-4.235652751636844</v>
+        <v>-17.02751779885972</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4808,18 +9794,354 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>53.15631490446475</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9.255477411270721</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-8.211339242959573</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-14.00670985783511</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8.66665234299983</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.499955118799418</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.682370311277764</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q4-25_prov vs c-to-c_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5.154210253965282</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-3.431919153777887</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8.1284334320178</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-4.235652751636844</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>-4.138795374940747</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -4836,7 +10158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5235,6 +10557,286 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.865586981141518</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.74122589244294</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>70.29235064004121</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.850111997520186</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-5.789373102848354</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1.713276288662723</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5.184033315081543</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.7472040368321289</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>7.861032328106851</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
